--- a/data/C1/1/circles.xlsx
+++ b/data/C1/1/circles.xlsx
@@ -115,26 +115,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="n">
-        <v>0</v>
+        <v>-0.41027925746262</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>0</v>
+        <v>0.113205712989721</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>-0.842041390335626</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0</v>
+        <v>0.619209972588491</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0.5</v>
@@ -142,13 +142,200 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>-0.325729211280716</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0</v>
+        <v>1.37009476406632</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>-0.427235657806364</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1.20190695204497</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>-0.131920442469862</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1.58000053133743</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>0.527852621222275</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1.37482824650172</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>0.549579762886611</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.0291807284153597</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>1.21159077456441</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>-0.227871173721373</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1.51606810837402</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.855737007108665</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>2.10973098725435</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.998382338572826</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>1.5175011117709</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.515376138556351</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1.10035501113153</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.717139283520032</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1.68990709917283</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.974007788927841</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>0.57175228410318</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1.81781331351006</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>0.380391634183395</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.75188856529696</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>0.664611280723378</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.899189108949054</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>0.721379605962881</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.909806739399665</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1.24676234375559</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.884336974993744</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>0.89173399058273</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.162309211257937</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>0.791475203330735</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.134032843985628</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
